--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119813412</v>
+        <v>119813893</v>
       </c>
       <c r="B3" t="n">
-        <v>74570</v>
+        <v>91005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1776</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461093</v>
+        <v>460994</v>
       </c>
       <c r="R3" t="n">
-        <v>7189320</v>
+        <v>7189400</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119813893</v>
+        <v>119813412</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>74570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460994</v>
+        <v>461093</v>
       </c>
       <c r="R4" t="n">
-        <v>7189400</v>
+        <v>7189320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119813475</v>
+        <v>119813415</v>
       </c>
       <c r="B5" t="n">
-        <v>77867</v>
+        <v>78997</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Liten sotlav</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461105</v>
+        <v>461093</v>
       </c>
       <c r="R5" t="n">
-        <v>7189345</v>
+        <v>7189320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1194,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119813415</v>
+        <v>119813475</v>
       </c>
       <c r="B7" t="n">
-        <v>78997</v>
+        <v>77867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,16 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6038705</v>
+        <v>498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461093</v>
+        <v>461105</v>
       </c>
       <c r="R7" t="n">
-        <v>7189320</v>
+        <v>7189345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119813415</v>
+        <v>119822165</v>
       </c>
       <c r="B5" t="n">
-        <v>78997</v>
+        <v>74506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,33 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6038705</v>
+        <v>229653</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461093</v>
+        <v>460854</v>
       </c>
       <c r="R5" t="n">
-        <v>7189320</v>
+        <v>7189523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1062,18 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en grov och gammal sälg i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822165</v>
+        <v>119813415</v>
       </c>
       <c r="B6" t="n">
-        <v>74506</v>
+        <v>78997</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1090,41 +1104,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229653</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Njurlavsknapp</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460854</v>
+        <v>461093</v>
       </c>
       <c r="R6" t="n">
-        <v>7189523</v>
+        <v>7189320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,18 +1165,12 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en grov och gammal sälg i sumpskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119814538</v>
+        <v>119813415</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>78997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460997</v>
+        <v>461093</v>
       </c>
       <c r="R2" t="n">
-        <v>7189481</v>
+        <v>7189320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119813893</v>
+        <v>119813412</v>
       </c>
       <c r="B3" t="n">
-        <v>91005</v>
+        <v>74570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1776</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460994</v>
+        <v>461093</v>
       </c>
       <c r="R3" t="n">
-        <v>7189400</v>
+        <v>7189320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119813412</v>
+        <v>119814538</v>
       </c>
       <c r="B4" t="n">
-        <v>74570</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1776</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461093</v>
+        <v>460997</v>
       </c>
       <c r="R4" t="n">
-        <v>7189320</v>
+        <v>7189481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822165</v>
+        <v>119813475</v>
       </c>
       <c r="B5" t="n">
-        <v>74506</v>
+        <v>77867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +988,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229653</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460854</v>
+        <v>461105</v>
       </c>
       <c r="R5" t="n">
-        <v>7189523</v>
+        <v>7189345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,18 +1054,12 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en grov och gammal sälg i sumpskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119813415</v>
+        <v>119813893</v>
       </c>
       <c r="B6" t="n">
-        <v>78997</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,16 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6038705</v>
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461093</v>
+        <v>460994</v>
       </c>
       <c r="R6" t="n">
-        <v>7189320</v>
+        <v>7189400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119813475</v>
+        <v>119822165</v>
       </c>
       <c r="B7" t="n">
-        <v>77867</v>
+        <v>74506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1192,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>229653</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461105</v>
+        <v>460854</v>
       </c>
       <c r="R7" t="n">
-        <v>7189345</v>
+        <v>7189523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,12 +1261,18 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en grov och gammal sälg i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119813415</v>
+        <v>119813893</v>
       </c>
       <c r="B2" t="n">
-        <v>78997</v>
+        <v>91005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6038705</v>
+        <v>1209</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461093</v>
+        <v>460994</v>
       </c>
       <c r="R2" t="n">
-        <v>7189320</v>
+        <v>7189400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119813412</v>
+        <v>119813475</v>
       </c>
       <c r="B3" t="n">
-        <v>74570</v>
+        <v>77867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1776</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461093</v>
+        <v>461105</v>
       </c>
       <c r="R3" t="n">
-        <v>7189320</v>
+        <v>7189345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119814538</v>
+        <v>119813415</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>78997</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -890,21 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460997</v>
+        <v>461093</v>
       </c>
       <c r="R4" t="n">
-        <v>7189481</v>
+        <v>7189320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119813475</v>
+        <v>119822165</v>
       </c>
       <c r="B5" t="n">
-        <v>77867</v>
+        <v>74506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -988,38 +988,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>229653</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461105</v>
+        <v>460854</v>
       </c>
       <c r="R5" t="n">
-        <v>7189345</v>
+        <v>7189523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,12 +1057,18 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en grov och gammal sälg i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1078,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119813893</v>
+        <v>119814538</v>
       </c>
       <c r="B6" t="n">
         <v>91005</v>
@@ -1118,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460994</v>
+        <v>460997</v>
       </c>
       <c r="R6" t="n">
-        <v>7189400</v>
+        <v>7189481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822165</v>
+        <v>119813412</v>
       </c>
       <c r="B7" t="n">
-        <v>74506</v>
+        <v>74570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1192,41 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229653</v>
+        <v>1776</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460854</v>
+        <v>461093</v>
       </c>
       <c r="R7" t="n">
-        <v>7189523</v>
+        <v>7189320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,18 +1267,12 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På en grov och gammal sälg i sumpskog.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119813893</v>
+        <v>119814538</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460994</v>
+        <v>460997</v>
       </c>
       <c r="R2" t="n">
-        <v>7189400</v>
+        <v>7189481</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119813475</v>
+        <v>119822165</v>
       </c>
       <c r="B3" t="n">
-        <v>77867</v>
+        <v>74522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>229653</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461105</v>
+        <v>460854</v>
       </c>
       <c r="R3" t="n">
-        <v>7189345</v>
+        <v>7189523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +858,18 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en grov och gammal sälg i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119813415</v>
+        <v>119813893</v>
       </c>
       <c r="B4" t="n">
-        <v>78997</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6038705</v>
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461093</v>
+        <v>460994</v>
       </c>
       <c r="R4" t="n">
-        <v>7189320</v>
+        <v>7189400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822165</v>
+        <v>119813412</v>
       </c>
       <c r="B5" t="n">
-        <v>74506</v>
+        <v>74586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -988,41 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229653</v>
+        <v>1776</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460854</v>
+        <v>461093</v>
       </c>
       <c r="R5" t="n">
-        <v>7189523</v>
+        <v>7189320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,18 +1068,12 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en grov och gammal sälg i sumpskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119814538</v>
+        <v>119813415</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>79013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1108,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460997</v>
+        <v>461093</v>
       </c>
       <c r="R6" t="n">
-        <v>7189481</v>
+        <v>7189320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119813412</v>
+        <v>119813475</v>
       </c>
       <c r="B7" t="n">
-        <v>74570</v>
+        <v>77883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1776</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461093</v>
+        <v>461105</v>
       </c>
       <c r="R7" t="n">
-        <v>7189320</v>
+        <v>7189345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119814538</v>
+        <v>119813415</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>79013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460997</v>
+        <v>461093</v>
       </c>
       <c r="R2" t="n">
-        <v>7189481</v>
+        <v>7189320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -990,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119813412</v>
+        <v>119814538</v>
       </c>
       <c r="B5" t="n">
-        <v>74586</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1776</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461093</v>
+        <v>460997</v>
       </c>
       <c r="R5" t="n">
-        <v>7189320</v>
+        <v>7189481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119813415</v>
+        <v>119813412</v>
       </c>
       <c r="B6" t="n">
-        <v>79013</v>
+        <v>74586</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,16 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6038705</v>
+        <v>1776</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Amerikansk sönderfallslav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119813415</v>
+        <v>119822165</v>
       </c>
       <c r="B2" t="n">
-        <v>79013</v>
+        <v>74522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6038705</v>
+        <v>229653</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Njurlavsknapp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cliostomum piceicola</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Holien &amp; Tønsberg</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461093</v>
+        <v>460854</v>
       </c>
       <c r="R2" t="n">
-        <v>7189320</v>
+        <v>7189523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +756,18 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en grov och gammal sälg i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822165</v>
+        <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>74522</v>
+        <v>79013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,41 +798,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229653</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Njurlavsknapp</t>
-        </is>
+        <v>6038705</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Cliostomum piceicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Småvattnet, Jmt</t>
+          <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460854</v>
+        <v>461093</v>
       </c>
       <c r="R3" t="n">
-        <v>7189523</v>
+        <v>7189320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,18 +859,12 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en grov och gammal sälg i sumpskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119813412</v>
+        <v>119813475</v>
       </c>
       <c r="B6" t="n">
-        <v>74586</v>
+        <v>77883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1776</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461093</v>
+        <v>461105</v>
       </c>
       <c r="R6" t="n">
-        <v>7189320</v>
+        <v>7189345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119813475</v>
+        <v>119813412</v>
       </c>
       <c r="B7" t="n">
-        <v>77883</v>
+        <v>74586</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>1776</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461105</v>
+        <v>461093</v>
       </c>
       <c r="R7" t="n">
-        <v>7189345</v>
+        <v>7189320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -789,12 +789,7 @@
         <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>79013</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,6 +810,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Småvattnet, Västra Småvattnet, Jmt</t>
@@ -865,8 +863,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal, sluten grannaturskog vid bäck</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>79439</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 64332-2023 artfynd.xlsx
+++ b/artfynd/A 64332-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119813415</v>
       </c>
       <c r="B3" t="n">
-        <v>79448</v>
+        <v>79451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
